--- a/models/6273_DCF_Model_20260906.xlsx
+++ b/models/6273_DCF_Model_20260906.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ryosuke0923\ryosuke-japanese-equity-research\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{322CE7E5-D090-4684-B8FD-D5697F1E7616}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3995E96A-7F77-45AA-AE42-EC2E91848140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -80,7 +80,7 @@
     <t>vs Current Price</t>
   </si>
   <si>
-    <t>DCF - Perpetuity Growth</t>
+    <t>DCF - Perpetuity Growth [参考・Target不算入 — 追補6 §X]</t>
   </si>
   <si>
     <t>DCF - Exit Multiple</t>
@@ -92,7 +92,7 @@
     <t>Comps - PER Median [参考・Target不算入]</t>
   </si>
   <si>
-    <t>Note: Target Mid は DCF 2法（PGM / Exit）の平均のみ。Comps 2法は [参考] で Target 不算入（EV&lt;ネットデットで株式価値が負になる手法は INVALID として平均から除外）</t>
+    <t>Note: Target Mid は DCF 2法（PGM / Exit）の平均のみ。Comps 2法は [参考] で Target 不算入（EV&lt;ネットデットで株式価値が負になる手法は INVALID として平均から除外） ■【追補6 §X】PGMとExitの乖離が **3.35倍** で 3.0倍を超えたため、**乖離そのものを裁定トリガーとする追補6 §X により中点平均を禁止**し、どちらの脚を落とすかを判定した。■**観測倍率バンドテスト**: Peer の実測 EV/EBITDA の第1〜第3四分位バンドは **(14.579873209990334, 18.258808221981813, 5)倍**。これに対し **PGM逆算 4.65倍 / 仮定Exit 15.60倍**。**PGM法のみがバンドの外にあるため PGM法を[参考]に降格し、Target = Exit 単独**とした。■バンドテストは市場倍率を無条件のアンカーにするものではない（それではスクリーナーが市場の複写に堕する）。**実際に取引されているレンジの外に出た脚だけを取り除く**という位置づけである。</t>
   </si>
   <si>
     <t>DCF Valuation Range (PGM - Exit)</t>
@@ -1627,7 +1627,7 @@
     <col min="3" max="5" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="45" t="s">
         <v>0</v>
       </c>
@@ -1635,19 +1635,19 @@
       <c r="D1" s="44"/>
       <c r="E1" s="44"/>
     </row>
-    <row r="3" spans="2:5" ht="18" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="43" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="44"/>
       <c r="D3" s="44"/>
     </row>
-    <row r="4" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
@@ -1655,7 +1655,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>5</v>
       </c>
@@ -1663,7 +1663,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>7</v>
       </c>
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
         <v>9</v>
       </c>
@@ -1679,16 +1679,16 @@
         <v>67140</v>
       </c>
     </row>
-    <row r="10" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <f>IF(COUNT(C16:C17)=0,"N/A",ROUND(AVERAGE(C16:C17),0))</f>
-        <v>41615</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+        <f>IF(ISNUMBER(C17),ROUND(C17,0),"N/A")</f>
+        <v>55711</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
         <v>11</v>
       </c>
@@ -1697,23 +1697,23 @@
         <v>SELL</v>
       </c>
     </row>
-    <row r="12" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="7">
         <f>IF(ISNUMBER(C10),(C10-C9)/C9,"N/A")</f>
-        <v>-0.38017575215966637</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+        <v>-0.17022639261245159</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="8" t="s">
         <v>13</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
     </row>
-    <row r="15" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="10" t="s">
         <v>14</v>
       </c>
@@ -1724,7 +1724,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="2:5" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>17</v>
       </c>
@@ -1737,7 +1737,7 @@
         <v>-0.59014000595770033</v>
       </c>
     </row>
-    <row r="17" spans="2:5" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>18</v>
       </c>
@@ -1750,7 +1750,7 @@
         <v>-0.17022639261245159</v>
       </c>
     </row>
-    <row r="18" spans="2:5" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>19</v>
       </c>
@@ -1763,7 +1763,7 @@
         <v>2.9818290140005959E-2</v>
       </c>
     </row>
-    <row r="19" spans="2:5" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>20</v>
       </c>
@@ -1776,7 +1776,7 @@
         <v>0.31979445933869527</v>
       </c>
     </row>
-    <row r="20" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="45" t="s">
         <v>21</v>
       </c>
@@ -1784,7 +1784,7 @@
       <c r="D20" s="44"/>
       <c r="E20" s="44"/>
     </row>
-    <row r="21" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
         <v>22</v>
       </c>
@@ -1793,7 +1793,7 @@
         <v>27518 - 55711</v>
       </c>
     </row>
-    <row r="23" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="8" t="s">
         <v>23</v>
       </c>
@@ -1815,10 +1815,10 @@
     <row r="26" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B26" t="str">
         <f>"At "&amp;TEXT(C9,"#,##0")&amp;" the shares are valued in line with the automation peer median on EV/EBITDA; a base case that halts the four-year margin slide supports "&amp;TEXT(C10,"#,##0")&amp;", or "&amp;TEXT(C12,"+0.0%;-0.0%")&amp;" from here."</f>
-        <v>At 67,140 the shares are valued in line with the automation peer median on EV/EBITDA; a base case that halts the four-year margin slide supports 41,615, or -38.0% from here.</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+        <v>At 67,140 the shares are valued in line with the automation peer median on EV/EBITDA; a base case that halts the four-year margin slide supports 55,711, or -17.0% from here.</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="8" t="s">
         <v>24</v>
       </c>
@@ -1828,7 +1828,7 @@
     <row r="29" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B29" t="str">
         <f>"Capital expenditure has climbed to eighteen percent of revenue against depreciation near five percent, and the free cash flow behind "&amp;TEXT(C10,"#,##0")&amp;" depends entirely on that spending tapering — a commitment the filings do not make."</f>
-        <v>Capital expenditure has climbed to eighteen percent of revenue against depreciation near five percent, and the free cash flow behind 41,615 depends entirely on that spending tapering — a commitment the filings do not make.</v>
+        <v>Capital expenditure has climbed to eighteen percent of revenue against depreciation near five percent, and the free cash flow behind 55,711 depends entirely on that spending tapering — a commitment the filings do not make.</v>
       </c>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.2">
@@ -1866,12 +1866,12 @@
     <col min="3" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="18" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="10" t="s">
         <v>27</v>
       </c>
@@ -1885,12 +1885,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>32</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>842541</v>
       </c>
     </row>
-    <row r="7" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>33</v>
       </c>
@@ -1924,7 +1924,7 @@
         <v>461089</v>
       </c>
     </row>
-    <row r="8" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>34</v>
       </c>
@@ -1945,7 +1945,7 @@
         <v>381452</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>35</v>
       </c>
@@ -1966,7 +1966,7 @@
         <v>0.45273998535382848</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
         <v>36</v>
       </c>
@@ -1983,7 +1983,7 @@
         <v>190893</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
         <v>37</v>
       </c>
@@ -2000,7 +2000,7 @@
         <v>190559</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
         <v>38</v>
       </c>
@@ -2017,7 +2017,7 @@
         <v>167304</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>39</v>
       </c>
@@ -2038,7 +2038,7 @@
         <v>0.22617178273816943</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>40</v>
       </c>
@@ -2059,7 +2059,7 @@
         <v>0.19857075204648794</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>41</v>
       </c>
@@ -2079,7 +2079,7 @@
         <v>6.3669348119195862E-2</v>
       </c>
     </row>
-    <row r="16" spans="2:6" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>43</v>
       </c>
@@ -2099,12 +2099,12 @@
         <v>1.6505032983784068E-3</v>
       </c>
     </row>
-    <row r="18" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
         <v>45</v>
       </c>
@@ -2121,7 +2121,7 @@
         <v>188917</v>
       </c>
     </row>
-    <row r="20" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
         <v>46</v>
       </c>
@@ -2138,7 +2138,7 @@
         <v>152701</v>
       </c>
     </row>
-    <row r="21" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
         <v>47</v>
       </c>
@@ -2159,7 +2159,7 @@
         <v>36216</v>
       </c>
     </row>
-    <row r="22" spans="2:6" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>48</v>
       </c>
@@ -2180,7 +2180,7 @@
         <v>4.2984258332828908E-2</v>
       </c>
     </row>
-    <row r="23" spans="2:6" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>49</v>
       </c>
@@ -2201,12 +2201,12 @@
         <v>0.18123865782199322</v>
       </c>
     </row>
-    <row r="25" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
         <v>51</v>
       </c>
@@ -2223,7 +2223,7 @@
         <v>663870</v>
       </c>
     </row>
-    <row r="27" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
         <v>52</v>
       </c>
@@ -2240,7 +2240,7 @@
         <v>5092</v>
       </c>
     </row>
-    <row r="28" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
         <v>53</v>
       </c>
@@ -2261,7 +2261,7 @@
         <v>-658778</v>
       </c>
     </row>
-    <row r="30" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
         <v>54</v>
       </c>
@@ -2285,12 +2285,12 @@
     <col min="3" max="7" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="18" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="8" t="s">
         <v>56</v>
       </c>
@@ -2300,7 +2300,7 @@
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
     </row>
-    <row r="5" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>57</v>
       </c>
@@ -2308,7 +2308,7 @@
         <v>5.57E-2</v>
       </c>
     </row>
-    <row r="6" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>58</v>
       </c>
@@ -2316,7 +2316,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="7" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>59</v>
       </c>
@@ -2324,7 +2324,7 @@
         <v>2.9700000000000001E-2</v>
       </c>
     </row>
-    <row r="8" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>60</v>
       </c>
@@ -2332,7 +2332,7 @@
         <v>1.3230999999999999</v>
       </c>
     </row>
-    <row r="9" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
         <v>61</v>
       </c>
@@ -2340,7 +2340,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="10" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
         <v>62</v>
       </c>
@@ -2348,7 +2348,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="11" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
         <v>63</v>
       </c>
@@ -2356,7 +2356,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="12" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
         <v>64</v>
       </c>
@@ -2364,7 +2364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
         <v>65</v>
       </c>
@@ -2372,7 +2372,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="14" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
         <v>66</v>
       </c>
@@ -2380,7 +2380,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="15" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
         <v>67</v>
       </c>
@@ -2388,7 +2388,7 @@
         <v>62477789</v>
       </c>
     </row>
-    <row r="16" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
         <v>68</v>
       </c>
@@ -2396,7 +2396,7 @@
         <v>-658778</v>
       </c>
     </row>
-    <row r="17" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
         <v>69</v>
       </c>
@@ -2404,7 +2404,7 @@
         <v>842541</v>
       </c>
     </row>
-    <row r="18" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
         <v>70</v>
       </c>
@@ -2412,7 +2412,7 @@
         <v>5.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="19" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
         <v>71</v>
       </c>
@@ -2420,7 +2420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
         <v>72</v>
       </c>
@@ -2428,7 +2428,7 @@
         <v>842541</v>
       </c>
     </row>
-    <row r="22" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="8" t="s">
         <v>73</v>
       </c>
@@ -2438,7 +2438,7 @@
       <c r="F22" s="9"/>
       <c r="G22" s="9"/>
     </row>
-    <row r="23" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
         <v>74</v>
       </c>
@@ -2447,7 +2447,7 @@
         <v>0.12570149999999999</v>
       </c>
     </row>
-    <row r="24" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
         <v>75</v>
       </c>
@@ -2456,7 +2456,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
         <v>76</v>
       </c>
@@ -2465,7 +2465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
         <v>77</v>
       </c>
@@ -2474,7 +2474,7 @@
         <v>0.12570149999999999</v>
       </c>
     </row>
-    <row r="27" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
         <v>78</v>
       </c>
@@ -2486,7 +2486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="8" t="s">
         <v>80</v>
       </c>
@@ -2496,7 +2496,7 @@
       <c r="F28" s="9"/>
       <c r="G28" s="9"/>
     </row>
-    <row r="29" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C29" s="10" t="s">
         <v>81</v>
       </c>
@@ -2513,7 +2513,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="30" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
         <v>41</v>
       </c>
@@ -2538,7 +2538,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="31" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="s">
         <v>86</v>
       </c>
@@ -2563,7 +2563,7 @@
         <v>0.54700000000000004</v>
       </c>
     </row>
-    <row r="32" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
         <v>87</v>
       </c>
@@ -2588,7 +2588,7 @@
         <v>0.2167</v>
       </c>
     </row>
-    <row r="33" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="4" t="s">
         <v>32</v>
       </c>
@@ -2613,7 +2613,7 @@
         <v>1005344.9994328651</v>
       </c>
     </row>
-    <row r="34" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="4" t="s">
         <v>33</v>
       </c>
@@ -2638,7 +2638,7 @@
         <v>549923.71468977723</v>
       </c>
     </row>
-    <row r="35" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="4" t="s">
         <v>34</v>
       </c>
@@ -2663,7 +2663,7 @@
         <v>455421.28474308783</v>
       </c>
     </row>
-    <row r="36" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="4" t="s">
         <v>35</v>
       </c>
@@ -2688,7 +2688,7 @@
         <v>0.45299999999999996</v>
       </c>
     </row>
-    <row r="37" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="4" t="s">
         <v>88</v>
       </c>
@@ -2713,7 +2713,7 @@
         <v>217858.26137710185</v>
       </c>
     </row>
-    <row r="38" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="4" t="s">
         <v>89</v>
       </c>
@@ -2738,7 +2738,7 @@
         <v>0.23629999999999995</v>
       </c>
     </row>
-    <row r="39" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="4" t="s">
         <v>90</v>
       </c>
@@ -2763,7 +2763,7 @@
         <v>237563.02336598598</v>
       </c>
     </row>
-    <row r="40" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="4" t="s">
         <v>91</v>
       </c>
@@ -2788,7 +2788,7 @@
         <v>59390.755841496495</v>
       </c>
     </row>
-    <row r="41" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="4" t="s">
         <v>92</v>
       </c>
@@ -2813,7 +2813,7 @@
         <v>178172.26752448949</v>
       </c>
     </row>
-    <row r="42" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="4" t="s">
         <v>93</v>
       </c>
@@ -2838,7 +2838,7 @@
         <v>53283.284969941844</v>
       </c>
     </row>
-    <row r="43" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="4" t="s">
         <v>94</v>
       </c>
@@ -2858,7 +2858,7 @@
         <v>56200</v>
       </c>
     </row>
-    <row r="44" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="4" t="s">
         <v>95</v>
       </c>
@@ -2883,7 +2883,7 @@
         <v>20240.990775083425</v>
       </c>
     </row>
-    <row r="45" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="4" t="s">
         <v>96</v>
       </c>
@@ -2908,7 +2908,7 @@
         <v>155014.5617193479</v>
       </c>
     </row>
-    <row r="46" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="4" t="s">
         <v>97</v>
       </c>
@@ -2933,7 +2933,7 @@
         <v>0.55320204395705053</v>
       </c>
     </row>
-    <row r="47" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="4" t="s">
         <v>98</v>
       </c>
@@ -2958,7 +2958,7 @@
         <v>85754.372386249612</v>
       </c>
     </row>
-    <row r="49" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="22" t="s">
         <v>99</v>
       </c>
@@ -2968,7 +2968,7 @@
       <c r="F49" s="23"/>
       <c r="G49" s="23"/>
     </row>
-    <row r="50" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="4" t="s">
         <v>100</v>
       </c>
@@ -2977,7 +2977,7 @@
         <v>311924.39546823862</v>
       </c>
     </row>
-    <row r="51" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="4" t="s">
         <v>101</v>
       </c>
@@ -2986,7 +2986,7 @@
         <v>1353177.8528069332</v>
       </c>
     </row>
-    <row r="52" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="4" t="s">
         <v>102</v>
       </c>
@@ -2995,7 +2995,7 @@
         <v>748580.7540102083</v>
       </c>
     </row>
-    <row r="53" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="4" t="s">
         <v>103</v>
       </c>
@@ -3004,7 +3004,7 @@
         <v>1060505.1494784469</v>
       </c>
     </row>
-    <row r="54" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="4" t="s">
         <v>104</v>
       </c>
@@ -3013,7 +3013,7 @@
         <v>1719283.1494784469</v>
       </c>
     </row>
-    <row r="55" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="4" t="s">
         <v>105</v>
       </c>
@@ -3022,7 +3022,7 @@
         <v>27518</v>
       </c>
     </row>
-    <row r="57" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="22" t="s">
         <v>106</v>
       </c>
@@ -3032,7 +3032,7 @@
       <c r="F57" s="23"/>
       <c r="G57" s="23"/>
     </row>
-    <row r="58" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="4" t="s">
         <v>100</v>
       </c>
@@ -3041,7 +3041,7 @@
         <v>311924.39546823862</v>
       </c>
     </row>
-    <row r="59" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="4" t="s">
         <v>107</v>
       </c>
@@ -3050,7 +3050,7 @@
         <v>290846.30833592784</v>
       </c>
     </row>
-    <row r="60" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="4" t="s">
         <v>108</v>
       </c>
@@ -3059,7 +3059,7 @@
         <v>4537202.4100404745</v>
       </c>
     </row>
-    <row r="61" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="4" t="s">
         <v>102</v>
       </c>
@@ -3068,7 +3068,7 @@
         <v>2509989.6470812461</v>
       </c>
     </row>
-    <row r="62" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="4" t="s">
         <v>103</v>
       </c>
@@ -3077,7 +3077,7 @@
         <v>2821914.0425494849</v>
       </c>
     </row>
-    <row r="63" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="4" t="s">
         <v>104</v>
       </c>
@@ -3086,7 +3086,7 @@
         <v>3480692.0425494849</v>
       </c>
     </row>
-    <row r="64" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="4" t="s">
         <v>109</v>
       </c>
@@ -3095,7 +3095,7 @@
         <v>55711</v>
       </c>
     </row>
-    <row r="66" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="22" t="s">
         <v>110</v>
       </c>
@@ -3105,7 +3105,7 @@
       <c r="F66" s="23"/>
       <c r="G66" s="23"/>
     </row>
-    <row r="67" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C67" s="25" t="s">
         <v>111</v>
       </c>
@@ -3122,12 +3122,12 @@
         <v>115</v>
       </c>
     </row>
-    <row r="68" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B68" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="69" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="4" t="s">
         <v>79</v>
       </c>
@@ -3147,7 +3147,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="70" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="4" t="s">
         <v>116</v>
       </c>
@@ -3167,7 +3167,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="71" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="4" t="s">
         <v>117</v>
       </c>
@@ -3187,7 +3187,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="72" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="4" t="s">
         <v>118</v>
       </c>
@@ -3207,7 +3207,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="73" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="4" t="s">
         <v>119</v>
       </c>
@@ -3227,12 +3227,12 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="75" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="3" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="76" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="4" t="s">
         <v>79</v>
       </c>
@@ -3252,7 +3252,7 @@
         <v>0.54700000000000004</v>
       </c>
     </row>
-    <row r="77" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="4" t="s">
         <v>116</v>
       </c>
@@ -3272,7 +3272,7 @@
         <v>0.54</v>
       </c>
     </row>
-    <row r="78" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="4" t="s">
         <v>117</v>
       </c>
@@ -3292,7 +3292,7 @@
         <v>0.54700000000000004</v>
       </c>
     </row>
-    <row r="79" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="4" t="s">
         <v>118</v>
       </c>
@@ -3312,7 +3312,7 @@
         <v>0.55500000000000005</v>
       </c>
     </row>
-    <row r="80" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B80" s="4" t="s">
         <v>119</v>
       </c>
@@ -3332,12 +3332,12 @@
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="82" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B82" s="3" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="83" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B83" s="4" t="s">
         <v>79</v>
       </c>
@@ -3357,7 +3357,7 @@
         <v>0.2167</v>
       </c>
     </row>
-    <row r="84" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="4" t="s">
         <v>116</v>
       </c>
@@ -3377,7 +3377,7 @@
         <v>0.1923</v>
       </c>
     </row>
-    <row r="85" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B85" s="4" t="s">
         <v>117</v>
       </c>
@@ -3397,7 +3397,7 @@
         <v>0.2167</v>
       </c>
     </row>
-    <row r="86" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B86" s="4" t="s">
         <v>118</v>
       </c>
@@ -3417,7 +3417,7 @@
         <v>0.251</v>
       </c>
     </row>
-    <row r="87" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B87" s="4" t="s">
         <v>119</v>
       </c>
@@ -3461,17 +3461,17 @@
     <col min="3" max="9" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="18" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="3" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="5" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="8" t="s">
         <v>122</v>
       </c>
@@ -3483,7 +3483,7 @@
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
     </row>
-    <row r="6" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>123</v>
       </c>
@@ -3492,7 +3492,7 @@
         <v>67140</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>67</v>
       </c>
@@ -3501,7 +3501,7 @@
         <v>62477789</v>
       </c>
     </row>
-    <row r="8" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>124</v>
       </c>
@@ -3510,7 +3510,7 @@
         <v>4194758.7534600003</v>
       </c>
     </row>
-    <row r="9" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
         <v>68</v>
       </c>
@@ -3519,7 +3519,7 @@
         <v>-658778</v>
       </c>
     </row>
-    <row r="10" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
         <v>125</v>
       </c>
@@ -3528,7 +3528,7 @@
         <v>3535980.7534600003</v>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
         <v>126</v>
       </c>
@@ -3537,7 +3537,7 @@
         <v>0.12570149999999999</v>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
         <v>127</v>
       </c>
@@ -3546,7 +3546,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="13" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
         <v>128</v>
       </c>
@@ -3555,7 +3555,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="14" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
         <v>129</v>
       </c>
@@ -3563,7 +3563,7 @@
         <v>190559</v>
       </c>
     </row>
-    <row r="15" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
         <v>130</v>
       </c>
@@ -3571,7 +3571,7 @@
         <v>258201</v>
       </c>
     </row>
-    <row r="16" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
         <v>131</v>
       </c>
@@ -3580,7 +3580,7 @@
         <v>1005344.9994328651</v>
       </c>
     </row>
-    <row r="17" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
         <v>132</v>
       </c>
@@ -3589,7 +3589,7 @@
         <v>1060505.1494784469</v>
       </c>
     </row>
-    <row r="18" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
         <v>133</v>
       </c>
@@ -3597,7 +3597,7 @@
         <v>0.31305742677976461</v>
       </c>
     </row>
-    <row r="19" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
         <v>134</v>
       </c>
@@ -3606,7 +3606,7 @@
         <v>2475475.6039815536</v>
       </c>
     </row>
-    <row r="20" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
         <v>135</v>
       </c>
@@ -3615,7 +3615,7 @@
         <v>39622</v>
       </c>
     </row>
-    <row r="22" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="8" t="s">
         <v>136</v>
       </c>
@@ -3627,12 +3627,12 @@
       <c r="H22" s="9"/>
       <c r="I22" s="9"/>
     </row>
-    <row r="23" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="24" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
         <v>138</v>
       </c>
@@ -3641,7 +3641,7 @@
         <v>409118.27714645222</v>
       </c>
     </row>
-    <row r="25" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
         <v>139</v>
       </c>
@@ -3650,7 +3650,7 @@
         <v>545491.03619526967</v>
       </c>
     </row>
-    <row r="26" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="6" t="s">
         <v>140</v>
       </c>
@@ -3659,7 +3659,7 @@
         <v>2.1126604319707116</v>
       </c>
     </row>
-    <row r="27" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="6" t="s">
         <v>141</v>
       </c>
@@ -3668,7 +3668,7 @@
         <v>2.8625834318781567</v>
       </c>
     </row>
-    <row r="28" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="6" t="s">
         <v>142</v>
       </c>
@@ -3677,7 +3677,7 @@
         <v>0.54259088820553336</v>
       </c>
     </row>
-    <row r="29" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="6" t="s">
         <v>143</v>
       </c>
@@ -3686,7 +3686,7 @@
         <v>1742463.1697973474</v>
       </c>
     </row>
-    <row r="32" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="8" t="s">
         <v>144</v>
       </c>
@@ -3698,17 +3698,17 @@
       <c r="H32" s="9"/>
       <c r="I32" s="9"/>
     </row>
-    <row r="33" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="34" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="1" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="36" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="28" t="s">
         <v>147</v>
       </c>
@@ -3736,12 +3736,12 @@
         <v>0.14570149999999998</v>
       </c>
     </row>
-    <row r="37" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="3" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="38" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="4" t="s">
         <v>150</v>
       </c>
@@ -3769,7 +3769,7 @@
         <v>0.83582785903687928</v>
       </c>
     </row>
-    <row r="39" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="4" t="s">
         <v>151</v>
       </c>
@@ -3797,7 +3797,7 @@
         <v>1.5374134010873648</v>
       </c>
     </row>
-    <row r="40" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="4" t="s">
         <v>152</v>
       </c>
@@ -3825,7 +3825,7 @@
         <v>2.1289044880583674</v>
       </c>
     </row>
-    <row r="41" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="4" t="s">
         <v>153</v>
       </c>
@@ -3853,12 +3853,12 @@
         <v>2.8513914817955275</v>
       </c>
     </row>
-    <row r="42" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="3" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="43" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="4" t="s">
         <v>150</v>
       </c>
@@ -3886,7 +3886,7 @@
         <v>6.4128277651390082</v>
       </c>
     </row>
-    <row r="44" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="4" t="s">
         <v>151</v>
       </c>
@@ -3914,7 +3914,7 @@
         <v>5.61947264610391</v>
       </c>
     </row>
-    <row r="45" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="4" t="s">
         <v>152</v>
       </c>
@@ -3942,7 +3942,7 @@
         <v>4.9580689087624386</v>
       </c>
     </row>
-    <row r="46" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="4" t="s">
         <v>153</v>
       </c>
@@ -3970,7 +3970,7 @@
         <v>4.1606548227662001</v>
       </c>
     </row>
-    <row r="47" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="22" t="s">
         <v>155</v>
       </c>
@@ -3982,7 +3982,7 @@
       <c r="H47" s="23"/>
       <c r="I47" s="23"/>
     </row>
-    <row r="48" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="4" t="s">
         <v>150</v>
       </c>
@@ -4010,7 +4010,7 @@
         <v>710352.22688915918</v>
       </c>
     </row>
-    <row r="49" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="4" t="s">
         <v>151</v>
       </c>
@@ -4038,7 +4038,7 @@
         <v>786848.39713227516</v>
       </c>
     </row>
-    <row r="50" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="4" t="s">
         <v>152</v>
       </c>
@@ -4066,7 +4066,7 @@
         <v>869080.11436834978</v>
       </c>
     </row>
-    <row r="51" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="4" t="s">
         <v>153</v>
       </c>
@@ -4094,7 +4094,7 @@
         <v>1002554.3749530738</v>
       </c>
     </row>
-    <row r="52" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="22" t="s">
         <v>156</v>
       </c>
@@ -4106,7 +4106,7 @@
       <c r="H52" s="23"/>
       <c r="I52" s="23"/>
     </row>
-    <row r="53" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="4" t="s">
         <v>150</v>
       </c>
@@ -4134,7 +4134,7 @@
         <v>2.7511598595247855</v>
       </c>
     </row>
-    <row r="54" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="4" t="s">
         <v>151</v>
       </c>
@@ -4162,7 +4162,7 @@
         <v>3.0474258315509046</v>
       </c>
     </row>
-    <row r="55" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="4" t="s">
         <v>152</v>
       </c>
@@ -4190,7 +4190,7 @@
         <v>3.3659053000118115</v>
       </c>
     </row>
-    <row r="56" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="4" t="s">
         <v>153</v>
       </c>
@@ -4218,7 +4218,7 @@
         <v>3.8828446634717673</v>
       </c>
     </row>
-    <row r="58" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="8" t="s">
         <v>157</v>
       </c>
@@ -4230,12 +4230,12 @@
       <c r="H58" s="9"/>
       <c r="I58" s="9"/>
     </row>
-    <row r="59" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="1" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="60" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="4" t="s">
         <v>159</v>
       </c>
@@ -4244,7 +4244,7 @@
         <v>649329.42918865732</v>
       </c>
     </row>
-    <row r="62" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="28" t="s">
         <v>160</v>
       </c>
@@ -4255,7 +4255,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="63" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="31">
         <v>0.1565</v>
       </c>
@@ -4268,7 +4268,7 @@
         <v>4.9244723224997866</v>
       </c>
     </row>
-    <row r="64" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="31">
         <v>0.23480000000000001</v>
       </c>
@@ -4281,7 +4281,7 @@
         <v>3.282282446640616</v>
       </c>
     </row>
-    <row r="65" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B65" s="4" t="s">
         <v>163</v>
       </c>
@@ -4294,7 +4294,7 @@
         <v>2.4617844923812928</v>
       </c>
     </row>
-    <row r="66" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="31">
         <v>0.39129999999999998</v>
       </c>
@@ -4307,7 +4307,7 @@
         <v>1.9695372309512309</v>
       </c>
     </row>
-    <row r="67" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B67" s="31">
         <v>0.46960000000000002</v>
       </c>
@@ -4320,7 +4320,7 @@
         <v>1.641141223320308</v>
       </c>
     </row>
-    <row r="69" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="8" t="s">
         <v>164</v>
       </c>
@@ -4332,7 +4332,7 @@
       <c r="H69" s="9"/>
       <c r="I69" s="9"/>
     </row>
-    <row r="70" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="6" t="s">
         <v>165</v>
       </c>
@@ -4341,7 +4341,7 @@
         <v>15.020839631528643</v>
       </c>
     </row>
-    <row r="71" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="6" t="s">
         <v>166</v>
       </c>
@@ -4350,7 +4350,7 @@
         <v>4.1968055601567169</v>
       </c>
     </row>
-    <row r="72" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="4" t="s">
         <v>167</v>
       </c>
@@ -4359,7 +4359,7 @@
         <v>5.9053647233552056</v>
       </c>
     </row>
-    <row r="73" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="4" t="s">
         <v>168</v>
       </c>
@@ -4368,7 +4368,7 @@
         <v>5.0326170907602332</v>
       </c>
     </row>
-    <row r="74" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="4" t="s">
         <v>169</v>
       </c>
@@ -4377,12 +4377,12 @@
         <v>15.552094158010673</v>
       </c>
     </row>
-    <row r="75" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="1" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="77" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="22" t="s">
         <v>171</v>
       </c>
@@ -4394,13 +4394,13 @@
       <c r="H77" s="23"/>
       <c r="I77" s="23"/>
     </row>
-    <row r="78" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="4" t="str">
         <f>"At "&amp;TEXT(C6,"#,##0")&amp;" yen the market is paying for a steady-state operating profit of "&amp;TEXT(F49,"#,##0")&amp;" mn JPY - "&amp;TEXT(F54,"0.00")&amp;"x the FY2023 cycle peak of "&amp;TEXT(C15,"#,##0")&amp;" mn - reached in 5 years and sustained for ever, against "&amp;TEXT(C14,"#,##0")&amp;" mn actually earned in FY2026."</f>
         <v>At 67,140 yen the market is paying for a steady-state operating profit of 649,329 mn JPY - 2.51x the FY2023 cycle peak of 258,201 mn - reached in 5 years and sustained for ever, against 190,559 mn actually earned in FY2026.</v>
       </c>
     </row>
-    <row r="79" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="4" t="str">
         <f>"Even with no ramp at all (Block A) the price needs "&amp;TEXT(C25,"#,##0")&amp;" mn, or "&amp;TEXT(C26,"0.00")&amp;"x the peak. The base case supports an EV of only "&amp;TEXT(C17,"#,##0")&amp;" mn, leaving "&amp;TEXT(C20,"#,##0")&amp;" yen per share of the current price unexplained by mid-cycle economics."</f>
         <v>Even with no ramp at all (Block A) the price needs 545,491 mn, or 2.11x the peak. The base case supports an EV of only 1,060,505 mn, leaving 39,622 yen per share of the current price unexplained by mid-cycle economics.</v>
@@ -4425,12 +4425,12 @@
     <col min="3" max="8" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="18" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="8" t="s">
         <v>173</v>
       </c>
@@ -4453,7 +4453,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="33" t="s">
         <v>175</v>
       </c>
@@ -4482,7 +4482,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="33" t="s">
         <v>176</v>
       </c>
@@ -4511,7 +4511,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="33" t="s">
         <v>177</v>
       </c>
@@ -4540,7 +4540,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="8" t="s">
         <v>178</v>
       </c>
@@ -4551,7 +4551,7 @@
       <c r="G8" s="9"/>
       <c r="H8" s="9"/>
     </row>
-    <row r="9" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="33" t="s">
         <v>32</v>
       </c>
@@ -4579,7 +4579,7 @@
         <v>1005344.9994328651</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="33" t="s">
         <v>33</v>
       </c>
@@ -4607,7 +4607,7 @@
         <v>549923.71468977723</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="8" t="s">
         <v>179</v>
       </c>
@@ -4618,7 +4618,7 @@
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
-    <row r="12" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="33" t="s">
         <v>180</v>
       </c>
@@ -4646,7 +4646,7 @@
         <v>275436.98614599044</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="33" t="s">
         <v>181</v>
       </c>
@@ -4674,7 +4674,7 @@
         <v>623749.09008648701</v>
       </c>
     </row>
-    <row r="14" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="33" t="s">
         <v>182</v>
       </c>
@@ -4703,7 +4703,7 @@
         <v>899186.07623247744</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="33" t="s">
         <v>183</v>
       </c>
@@ -4731,7 +4731,7 @@
         <v>69305.454454054125</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="33" t="s">
         <v>184</v>
       </c>
@@ -4760,7 +4760,7 @@
         <v>69305.454454054125</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="22" t="s">
         <v>185</v>
       </c>
@@ -4771,7 +4771,7 @@
       <c r="G17" s="23"/>
       <c r="H17" s="23"/>
     </row>
-    <row r="18" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="33" t="s">
         <v>186</v>
       </c>
@@ -4800,7 +4800,7 @@
         <v>829880.62177842332</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="33" t="s">
         <v>95</v>
       </c>
@@ -4828,7 +4828,7 @@
         <v>20240.990775083425</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="22" t="s">
         <v>187</v>
       </c>
@@ -4839,7 +4839,7 @@
       <c r="G22" s="23"/>
       <c r="H22" s="23"/>
     </row>
-    <row r="23" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D23" s="25" t="s">
         <v>81</v>
       </c>
@@ -4856,12 +4856,12 @@
         <v>85</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="3" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="25" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
         <v>79</v>
       </c>
@@ -4881,7 +4881,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
         <v>116</v>
       </c>
@@ -4901,7 +4901,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
         <v>117</v>
       </c>
@@ -4921,7 +4921,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
         <v>118</v>
       </c>
@@ -4941,7 +4941,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="29" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
         <v>119</v>
       </c>
@@ -4961,12 +4961,12 @@
         <v>110</v>
       </c>
     </row>
-    <row r="31" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="3" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="32" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
         <v>79</v>
       </c>
@@ -4986,7 +4986,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="4" t="s">
         <v>116</v>
       </c>
@@ -5006,7 +5006,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="34" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="4" t="s">
         <v>117</v>
       </c>
@@ -5026,7 +5026,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="4" t="s">
         <v>118</v>
       </c>
@@ -5046,7 +5046,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="4" t="s">
         <v>119</v>
       </c>
@@ -5066,12 +5066,12 @@
         <v>456</v>
       </c>
     </row>
-    <row r="38" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="3" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="39" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="4" t="s">
         <v>79</v>
       </c>
@@ -5091,7 +5091,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="4" t="s">
         <v>116</v>
       </c>
@@ -5111,7 +5111,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="4" t="s">
         <v>117</v>
       </c>
@@ -5131,7 +5131,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="4" t="s">
         <v>118</v>
       </c>
@@ -5151,7 +5151,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="43" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="4" t="s">
         <v>119</v>
       </c>
@@ -5192,17 +5192,17 @@
     <col min="17" max="17" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:17" ht="18" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="3" spans="2:17" ht="14" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="4" spans="2:17" ht="28" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:17" ht="28" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="10" t="s">
         <v>3</v>
       </c>
@@ -5252,7 +5252,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="5" spans="2:17" ht="14" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>207</v>
       </c>
@@ -5307,7 +5307,7 @@
         <v>2115090</v>
       </c>
     </row>
-    <row r="6" spans="2:17" ht="14" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>209</v>
       </c>
@@ -5360,7 +5360,7 @@
         <v>1864871</v>
       </c>
     </row>
-    <row r="7" spans="2:17" ht="14" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>211</v>
       </c>
@@ -5413,7 +5413,7 @@
         <v>4484266</v>
       </c>
     </row>
-    <row r="8" spans="2:17" ht="14" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>213</v>
       </c>
@@ -5466,7 +5466,7 @@
         <v>3254652</v>
       </c>
     </row>
-    <row r="9" spans="2:17" ht="14" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
         <v>215</v>
       </c>
@@ -5519,7 +5519,7 @@
         <v>835885</v>
       </c>
     </row>
-    <row r="10" spans="2:17" ht="14" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
         <v>217</v>
       </c>
@@ -5572,12 +5572,12 @@
         <v>483542</v>
       </c>
     </row>
-    <row r="14" spans="2:17" ht="14" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="15" spans="2:17" ht="14" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
         <v>220</v>
       </c>
@@ -5606,7 +5606,7 @@
         <v>7.2878881255402844E-2</v>
       </c>
     </row>
-    <row r="16" spans="2:17" ht="14" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
         <v>221</v>
       </c>
@@ -5635,7 +5635,7 @@
         <v>8.4564801398121822E-2</v>
       </c>
     </row>
-    <row r="17" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
         <v>222</v>
       </c>
@@ -5664,7 +5664,7 @@
         <v>8.9305372864932744E-2</v>
       </c>
     </row>
-    <row r="19" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="22" t="s">
         <v>223</v>
       </c>
@@ -5676,12 +5676,12 @@
       <c r="H19" s="23"/>
       <c r="I19" s="23"/>
     </row>
-    <row r="20" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="21" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
         <v>225</v>
       </c>
@@ -5689,7 +5689,7 @@
         <v>235405</v>
       </c>
     </row>
-    <row r="22" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
         <v>226</v>
       </c>
@@ -5697,7 +5697,7 @@
         <v>167302</v>
       </c>
     </row>
-    <row r="23" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
         <v>227</v>
       </c>
@@ -5705,7 +5705,7 @@
         <v>62477789</v>
       </c>
     </row>
-    <row r="24" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
         <v>68</v>
       </c>
@@ -5713,12 +5713,12 @@
         <v>-658778</v>
       </c>
     </row>
-    <row r="26" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="3" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="27" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
         <v>229</v>
       </c>
@@ -5727,7 +5727,7 @@
         <v>69142</v>
       </c>
     </row>
-    <row r="28" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
         <v>230</v>
       </c>
@@ -5755,12 +5755,12 @@
     <col min="3" max="9" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="18" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="3" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
         <v>232</v>
       </c>
@@ -5783,12 +5783,12 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="5" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="40" t="s">
         <v>236</v>
       </c>
@@ -5821,7 +5821,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="39">
         <f>$C$3-0.015</f>
         <v>0.11070149999999999</v>
@@ -5855,7 +5855,7 @@
         <v>31798</v>
       </c>
     </row>
-    <row r="8" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="39">
         <f>$C$3-0.01</f>
         <v>0.1157015</v>
@@ -5889,7 +5889,7 @@
         <v>30563</v>
       </c>
     </row>
-    <row r="9" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="39">
         <f>$C$3-0.005</f>
         <v>0.12070149999999999</v>
@@ -5923,7 +5923,7 @@
         <v>29451</v>
       </c>
     </row>
-    <row r="10" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="39">
         <f>$C$3</f>
         <v>0.12570149999999999</v>
@@ -5957,7 +5957,7 @@
         <v>28444</v>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="39">
         <f>$C$3+0.005</f>
         <v>0.1307015</v>
@@ -5991,7 +5991,7 @@
         <v>27528</v>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="39">
         <f>$C$3+0.01</f>
         <v>0.1357015</v>
@@ -6025,7 +6025,7 @@
         <v>26692</v>
       </c>
     </row>
-    <row r="13" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="39">
         <f>$C$3+0.015</f>
         <v>0.14070149999999998</v>
@@ -6059,12 +6059,12 @@
         <v>25925</v>
       </c>
     </row>
-    <row r="16" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="17" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="40" t="s">
         <v>238</v>
       </c>
@@ -6097,7 +6097,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="18" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="39">
         <f>$C$3-0.015</f>
         <v>0.11070149999999999</v>
@@ -6131,7 +6131,7 @@
         <v>66996</v>
       </c>
     </row>
-    <row r="19" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="39">
         <f>$C$3-0.01</f>
         <v>0.1157015</v>
@@ -6165,7 +6165,7 @@
         <v>65778</v>
       </c>
     </row>
-    <row r="20" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="39">
         <f>$C$3-0.005</f>
         <v>0.12070149999999999</v>
@@ -6199,7 +6199,7 @@
         <v>64592</v>
       </c>
     </row>
-    <row r="21" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="39">
         <f>$C$3</f>
         <v>0.12570149999999999</v>
@@ -6233,7 +6233,7 @@
         <v>63437</v>
       </c>
     </row>
-    <row r="22" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="39">
         <f>$C$3+0.005</f>
         <v>0.1307015</v>
@@ -6267,7 +6267,7 @@
         <v>62311</v>
       </c>
     </row>
-    <row r="23" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="39">
         <f>$C$3+0.01</f>
         <v>0.1357015</v>
@@ -6301,7 +6301,7 @@
         <v>61215</v>
       </c>
     </row>
-    <row r="24" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="39">
         <f>$C$3+0.015</f>
         <v>0.14070149999999998</v>
@@ -6335,7 +6335,7 @@
         <v>60147</v>
       </c>
     </row>
-    <row r="26" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="45" t="s">
         <v>239</v>
       </c>
@@ -6372,12 +6372,12 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="18" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="4" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="10" t="s">
         <v>241</v>
       </c>
@@ -6437,12 +6437,12 @@
         <v>256</v>
       </c>
     </row>
-    <row r="12" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="8" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="13" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="10" t="s">
         <v>258</v>
       </c>
@@ -6450,7 +6450,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="14" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
         <v>260</v>
       </c>
@@ -6458,7 +6458,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="15" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
         <v>262</v>
       </c>
@@ -6466,7 +6466,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="16" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
         <v>264</v>
       </c>
@@ -6474,7 +6474,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="17" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
         <v>266</v>
       </c>
@@ -6482,7 +6482,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="18" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
         <v>267</v>
       </c>
@@ -6490,7 +6490,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="19" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
         <v>269</v>
       </c>
@@ -6498,7 +6498,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="20" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
         <v>271</v>
       </c>
@@ -6506,7 +6506,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="21" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
         <v>273</v>
       </c>
@@ -6514,7 +6514,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="22" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
         <v>275</v>
       </c>
@@ -6522,7 +6522,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="23" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
         <v>277</v>
       </c>
@@ -6530,7 +6530,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
         <v>278</v>
       </c>
@@ -6538,7 +6538,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="25" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
         <v>279</v>
       </c>
@@ -6546,7 +6546,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="26" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
         <v>281</v>
       </c>
@@ -6554,7 +6554,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="27" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
         <v>282</v>
       </c>
@@ -6562,7 +6562,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="28" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
         <v>283</v>
       </c>
@@ -6570,7 +6570,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="29" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
         <v>285</v>
       </c>
@@ -6578,7 +6578,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="30" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
         <v>287</v>
       </c>
@@ -6586,7 +6586,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="31" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="s">
         <v>289</v>
       </c>
@@ -6594,7 +6594,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="32" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
         <v>290</v>
       </c>
@@ -6602,7 +6602,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="33" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="4" t="s">
         <v>291</v>
       </c>
@@ -6610,7 +6610,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="34" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="4" t="s">
         <v>292</v>
       </c>
@@ -6618,7 +6618,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="35" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="4" t="s">
         <v>294</v>
       </c>
@@ -6626,7 +6626,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="36" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="4" t="s">
         <v>296</v>
       </c>
@@ -6634,7 +6634,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="37" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="4" t="s">
         <v>298</v>
       </c>
@@ -6642,7 +6642,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="38" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="4" t="s">
         <v>300</v>
       </c>
@@ -6650,7 +6650,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="39" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="4" t="s">
         <v>302</v>
       </c>
@@ -6658,7 +6658,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="40" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="4" t="s">
         <v>304</v>
       </c>
@@ -6666,7 +6666,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="41" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="4" t="s">
         <v>305</v>
       </c>
@@ -6674,7 +6674,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="42" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="4" t="s">
         <v>307</v>
       </c>
@@ -6682,7 +6682,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="43" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="4" t="s">
         <v>309</v>
       </c>
@@ -6690,7 +6690,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="44" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="4" t="s">
         <v>311</v>
       </c>
@@ -6698,7 +6698,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="45" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="4" t="s">
         <v>313</v>
       </c>
@@ -6706,7 +6706,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="46" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="4" t="s">
         <v>315</v>
       </c>
@@ -6714,7 +6714,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="47" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="4" t="s">
         <v>317</v>
       </c>
@@ -6722,7 +6722,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="48" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="4" t="s">
         <v>319</v>
       </c>
@@ -6730,7 +6730,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="49" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="4" t="s">
         <v>321</v>
       </c>
@@ -6738,7 +6738,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="50" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="4" t="s">
         <v>323</v>
       </c>
@@ -6746,7 +6746,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="51" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="4" t="s">
         <v>325</v>
       </c>
@@ -6754,7 +6754,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="52" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="4" t="s">
         <v>327</v>
       </c>
@@ -6762,7 +6762,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="53" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="4" t="s">
         <v>329</v>
       </c>
@@ -6770,7 +6770,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="54" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="4" t="s">
         <v>331</v>
       </c>
@@ -6778,7 +6778,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="55" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="4" t="s">
         <v>333</v>
       </c>
@@ -6786,7 +6786,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="56" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="4" t="s">
         <v>335</v>
       </c>
@@ -6794,7 +6794,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="57" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="4" t="s">
         <v>337</v>
       </c>
@@ -6802,7 +6802,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="58" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="4" t="s">
         <v>339</v>
       </c>
@@ -6810,7 +6810,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="59" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="4" t="s">
         <v>341</v>
       </c>
@@ -6818,7 +6818,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="60" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="4" t="s">
         <v>343</v>
       </c>
